--- a/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,77</t>
+          <t>1,34; 11,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 14,54</t>
+          <t>3,04; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 10,76</t>
+          <t>2,81; 10,56</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,79</t>
+          <t>0,85; 2,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,55</t>
+          <t>1,48; 4,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,2</t>
+          <t>1,44; 3,23</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,33</t>
+          <t>0,85; 2,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,74</t>
+          <t>1,61; 3,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,79</t>
+          <t>1,4; 2,68</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4348</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6572</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>697; 5765</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1826; 9545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3152; 11862</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7226</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13479</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20705</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3814; 12615</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7455; 23345</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13713; 30843</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2518</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18253</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27703</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5561; 15312</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11953; 27301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19501; 37362</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,05</t>
+          <t>1,22; 11,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 15,88</t>
+          <t>2,76; 14,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,56</t>
+          <t>2,67; 10,63</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,8</t>
+          <t>0,85; 2,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,63</t>
+          <t>1,56; 4,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,23</t>
+          <t>1,44; 3,16</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,35</t>
+          <t>0,84; 2,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,67</t>
+          <t>1,54; 3,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,68</t>
+          <t>1,42; 2,72</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>697; 5765</t>
+          <t>638; 5938</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1826; 9545</t>
+          <t>1659; 8599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3152; 11862</t>
+          <t>3003; 11938</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3814; 12615</t>
+          <t>3829; 12387</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7455; 23345</t>
+          <t>7840; 22898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13713; 30843</t>
+          <t>13719; 30181</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2299</t>
+          <t>0; 2229</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2518</t>
+          <t>0; 2526</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5561; 15312</t>
+          <t>5503; 14974</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11953; 27301</t>
+          <t>11441; 27479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19501; 37362</t>
+          <t>19836; 37938</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,38</t>
+          <t>3,1; 15,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 14,31</t>
+          <t>1,49; 12,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,63</t>
+          <t>2,9; 11,65</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,75</t>
+          <t>1,68; 4,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,55</t>
+          <t>0,82; 2,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,16</t>
+          <t>1,47; 3,28</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,12</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,24</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,3</t>
+          <t>1,55; 3,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,69</t>
+          <t>0,87; 2,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,72</t>
+          <t>1,48; 2,84</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6369</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>638; 5938</t>
+          <t>1698; 8308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1659; 8599</t>
+          <t>663; 5632</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3003; 11938</t>
+          <t>2879; 11562</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>19635</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3829; 12387</t>
+          <t>7762; 21095</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7840; 22898</t>
+          <t>3452; 12337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13719; 30181</t>
+          <t>13001; 29056</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>357</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 1859</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2229</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2526</t>
+          <t>0; 1774</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>26362</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5503; 14974</t>
+          <t>10614; 25844</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11441; 27479</t>
+          <t>5391; 15045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19836; 37938</t>
+          <t>19253; 36980</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3,1; 15,15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 12,68</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,9; 11,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 4,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 2,92</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 3,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,12</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,56</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 3,78</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 2,44</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 2,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.07511202480868948</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.05067240974761767</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.06417335872074584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4118</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2251</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6369</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.03096603694589179</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01492960835177356</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.02900945550431111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1698; 8308</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>663; 5632</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2879; 11562</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1515326575889955</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1267906001130594</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1165016423926518</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.02747535077563819</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01636225280480418</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.02216962286344153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12716</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6919</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19635</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01677166948756581</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.008164345507281227</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01467919425781915</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7762; 21095</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3452; 12337</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13001; 29056</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04557925974851812</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.02917575487052794</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.03280679394072569</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,47 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.002160669986359485</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.001134501857426296</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0; 1859</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 1774</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.01123615589154532</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.00562953709421145</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.02516791528644101</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01486395680080411</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.02027821920810732</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>17192</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9170</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26362</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.01553903643119006</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.008737983143996084</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01481036645547883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>10614; 25844</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5391; 15045</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>19253; 36980</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.03783487268015984</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.02438814627909491</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02844623123686095</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4118</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2251</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>663</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8308</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5632</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>11562</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>12716</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6919</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>19635</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>7762</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3452</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>21095</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>12337</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>29056</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>357</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>17192</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9170</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>26362</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>10614</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5391</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>19253</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>25844</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>15045</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>36980</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>